--- a/r5-core-64-adding-related-person/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/r5-core-64-adding-related-person/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-ext-address-additionalInformation</t>
+    <t>https://fhir.hl7.at/core/r5/StructureDefinition/at-core-ext-address-additionalInformation</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-07T11:38:17+00:00</t>
+    <t>2026-10-13T17:05:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -135,7 +135,7 @@
     <t>element:Address.line</t>
   </si>
   <si>
-    <t>element:http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-address#Address.line</t>
+    <t>element:https://fhir.hl7.at/core/r5/StructureDefinition/at-core-address#Address.line</t>
   </si>
   <si>
     <t>ID</t>

--- a/r5-core-64-adding-related-person/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/r5-core-64-adding-related-person/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T17:05:56+00:00</t>
+    <t>2026-10-13T17:36:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
